--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>295</v>
+        <v>395</v>
       </c>
       <c r="E2">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>289</v>
+        <v>418</v>
       </c>
       <c r="E3">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>0</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,10 +450,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E3">
         <v>0</v>
